--- a/Data/Excel/Item.xlsx
+++ b/Data/Excel/Item.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\ProjectBB\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D2DDF9-0630-4A1C-A875-B37F21D4C0FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45255A7D-54E0-4588-BBAE-BCB95C378673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2124" yWindow="4032" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시트1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="106">
   <si>
     <t>ID</t>
   </si>
@@ -37,83 +37,19 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Item1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item2</t>
-  </si>
-  <si>
-    <t>Item3</t>
-  </si>
-  <si>
-    <t>Item4</t>
-  </si>
-  <si>
-    <t>Item5</t>
-  </si>
-  <si>
-    <t>고기</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>치즈</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>이것은 고기의 설명</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>이것은 치즈의 설명</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>이것은 피자의 설명</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Cooking/Ingredients/item_recipe_bear_meat.png</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Cooking/Ingredients/item_recipe_aged_cheese.png</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>우유</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Cooking/Ingredients/item_recipe_fresh_milk.png</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>버터</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>이것은 버터의 설명</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Cooking/Ingredients/item_recipe_butter.png</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>썬고기</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>이것은 썬 고기의 설명</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Cooking/Ingredients/item_recipe_bear_meat_chop.png</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -132,12 +68,339 @@
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID_Dev</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>신선한 우유</t>
+  </si>
+  <si>
+    <t>숙성 치즈</t>
+  </si>
+  <si>
+    <t>버터</t>
+  </si>
+  <si>
+    <t>야생 베리</t>
+  </si>
+  <si>
+    <t>이끼 버섯</t>
+  </si>
+  <si>
+    <t>사과</t>
+  </si>
+  <si>
+    <t>바다새 알</t>
+  </si>
+  <si>
+    <t>거친 보리</t>
+  </si>
+  <si>
+    <t>호밀</t>
+  </si>
+  <si>
+    <t>파슬리</t>
+  </si>
+  <si>
+    <t>야생 마늘</t>
+  </si>
+  <si>
+    <t>멧돼지 고기</t>
+  </si>
+  <si>
+    <t>양 고기</t>
+  </si>
+  <si>
+    <t>순록 고기</t>
+  </si>
+  <si>
+    <t>토끼 고기</t>
+  </si>
+  <si>
+    <t>바다새 고기</t>
+  </si>
+  <si>
+    <t>곰 고기</t>
+  </si>
+  <si>
+    <t>헤이즐넛</t>
+  </si>
+  <si>
+    <t>호두</t>
+  </si>
+  <si>
+    <t>말린 청어</t>
+  </si>
+  <si>
+    <t>말린 대구</t>
+  </si>
+  <si>
+    <t>홍합</t>
+  </si>
+  <si>
+    <t>순무</t>
+  </si>
+  <si>
+    <t>양배추</t>
+  </si>
+  <si>
+    <t>콩</t>
+  </si>
+  <si>
+    <t>당근</t>
+  </si>
+  <si>
+    <t>숲의 벌꿀</t>
+  </si>
+  <si>
+    <t>소금</t>
+  </si>
+  <si>
+    <t>태양석 가루</t>
+  </si>
+  <si>
+    <t>세계수 수액</t>
+  </si>
+  <si>
+    <t>fresh_milk</t>
+  </si>
+  <si>
+    <t>aged_cheese</t>
+  </si>
+  <si>
+    <t>butter</t>
+  </si>
+  <si>
+    <t>wild_berry</t>
+  </si>
+  <si>
+    <t>moss_mushroom</t>
+  </si>
+  <si>
+    <t>apple</t>
+  </si>
+  <si>
+    <t>seabird_egg</t>
+  </si>
+  <si>
+    <t>coarse_barley</t>
+  </si>
+  <si>
+    <t>rye</t>
+  </si>
+  <si>
+    <t>parsley</t>
+  </si>
+  <si>
+    <t>wild_garlic</t>
+  </si>
+  <si>
+    <t>boar_meat</t>
+  </si>
+  <si>
+    <t>mutton</t>
+  </si>
+  <si>
+    <t>reindeer_meat</t>
+  </si>
+  <si>
+    <t>rabbit_meat</t>
+  </si>
+  <si>
+    <t>seabird_meat</t>
+  </si>
+  <si>
+    <t>bear_meat</t>
+  </si>
+  <si>
+    <t>hazelnut</t>
+  </si>
+  <si>
+    <t>walnut</t>
+  </si>
+  <si>
+    <t>dried_herring</t>
+  </si>
+  <si>
+    <t>dried_cod</t>
+  </si>
+  <si>
+    <t>mussel</t>
+  </si>
+  <si>
+    <t>turnip</t>
+  </si>
+  <si>
+    <t>cabbage</t>
+  </si>
+  <si>
+    <t>bean</t>
+  </si>
+  <si>
+    <t>carrot</t>
+  </si>
+  <si>
+    <t>forest_honey</t>
+  </si>
+  <si>
+    <t>salt</t>
+  </si>
+  <si>
+    <t>unidentified_dried_meat</t>
+  </si>
+  <si>
+    <t>sunstone_powder</t>
+  </si>
+  <si>
+    <t>worldtree_sap</t>
+  </si>
+  <si>
+    <t>STR_fresh_milk</t>
+  </si>
+  <si>
+    <t>STR_aged_cheese</t>
+  </si>
+  <si>
+    <t>STR_butter</t>
+  </si>
+  <si>
+    <t>STR_wild_berry</t>
+  </si>
+  <si>
+    <t>STR_moss_mushroom</t>
+  </si>
+  <si>
+    <t>STR_apple</t>
+  </si>
+  <si>
+    <t>STR_seabird_egg</t>
+  </si>
+  <si>
+    <t>STR_coarse_barley</t>
+  </si>
+  <si>
+    <t>STR_rye</t>
+  </si>
+  <si>
+    <t>STR_parsley</t>
+  </si>
+  <si>
+    <t>STR_wild_garlic</t>
+  </si>
+  <si>
+    <t>STR_boar_meat</t>
+  </si>
+  <si>
+    <t>STR_mutton</t>
+  </si>
+  <si>
+    <t>STR_reindeer_meat</t>
+  </si>
+  <si>
+    <t>STR_rabbit_meat</t>
+  </si>
+  <si>
+    <t>STR_seabird_meat</t>
+  </si>
+  <si>
+    <t>STR_bear_meat</t>
+  </si>
+  <si>
+    <t>STR_hazelnut</t>
+  </si>
+  <si>
+    <t>STR_walnut</t>
+  </si>
+  <si>
+    <t>STR_dried_herring</t>
+  </si>
+  <si>
+    <t>STR_dried_cod</t>
+  </si>
+  <si>
+    <t>STR_mussel</t>
+  </si>
+  <si>
+    <t>STR_turnip</t>
+  </si>
+  <si>
+    <t>STR_cabbage</t>
+  </si>
+  <si>
+    <t>STR_bean</t>
+  </si>
+  <si>
+    <t>STR_carrot</t>
+  </si>
+  <si>
+    <t>STR_forest_honey</t>
+  </si>
+  <si>
+    <t>STR_salt</t>
+  </si>
+  <si>
+    <t>STR_unidentified_dried_meat</t>
+  </si>
+  <si>
+    <t>STR_sunstone_powder</t>
+  </si>
+  <si>
+    <t>STR_worldtree_sap</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>정체불명의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>말린고기</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>id:BBString</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -165,6 +428,28 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -174,7 +459,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -217,13 +502,28 @@
         <color rgb="FFCCCCCC"/>
       </left>
       <right style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
       </right>
       <top style="medium">
         <color rgb="FFCCCCCC"/>
       </top>
       <bottom style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="FFCCCCCC"/>
       </bottom>
       <diagonal/>
     </border>
@@ -231,7 +531,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -240,8 +540,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -461,110 +776,508 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="16.77734375" customWidth="1"/>
-    <col min="3" max="3" width="34.109375" customWidth="1"/>
-    <col min="4" max="4" width="65.21875" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="65.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" thickBot="1">
+    <row r="1" spans="1:5" ht="18" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="13.8" thickBot="1">
+    <row r="2" spans="1:5" ht="13.8" thickBot="1">
       <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A3" s="4">
+        <v>101001</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A4" s="6">
+        <v>101002</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A5" s="6">
+        <v>101003</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A6" s="6">
+        <v>102001</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A7" s="6">
+        <v>102002</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A8" s="6">
+        <v>102003</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A9" s="6">
+        <v>102004</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A10" s="6">
+        <v>103001</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A11" s="6">
+        <v>103002</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A12" s="6">
+        <v>104001</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A13" s="6">
+        <v>104002</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A14" s="6">
+        <v>105001</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A15" s="6">
+        <v>105002</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A16" s="6">
+        <v>105003</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C16" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A17" s="6">
+        <v>105004</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="18" thickBot="1">
-      <c r="A3" s="3" t="s">
+      <c r="C17" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="18" thickBot="1">
-      <c r="A4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A6" s="3" t="s">
+    </row>
+    <row r="18" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A18" s="6">
+        <v>105005</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A19" s="6">
+        <v>105006</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A20" s="6">
+        <v>106001</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A21" s="6">
+        <v>106002</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A22" s="6">
+        <v>107001</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A23" s="6">
+        <v>107002</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A24" s="6">
+        <v>107003</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A25" s="6">
+        <v>108001</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A26" s="6">
+        <v>108002</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A27" s="6">
+        <v>108003</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A28" s="6">
+        <v>108004</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A29" s="6">
+        <v>110001</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A30" s="6">
+        <v>110002</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A31" s="6">
+        <v>120001</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E31" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>17</v>
+    </row>
+    <row r="32" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A32" s="6">
+        <v>120002</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A33" s="6">
+        <v>120003</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
